--- a/TestComponents/TestSets/Losses/FieldConfigs.xlsx
+++ b/TestComponents/TestSets/Losses/FieldConfigs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\FieldNBalance\TestComponents\TestSets\Losses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEA7AF8-C4AA-4AF1-A150-E53F73000165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67F0F86-BFDF-4C3B-AEEC-009E96ED6B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D0D9F3F3-C1B3-4B79-AF5D-93A117BC34BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0D9F3F3-C1B3-4B79-AF5D-93A117BC34BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="83">
   <si>
     <t>SampleDepth</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>Top30cm</t>
+  </si>
+  <si>
+    <t>FinalFertDate</t>
   </si>
 </sst>
 </file>
@@ -682,14 +685,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67FC6C2-7F6C-4E8B-9465-EDB17589DEC5}">
-  <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="17" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>46</v>
       </c>
@@ -739,7 +742,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
@@ -792,7 +795,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" t="s">
         <v>54</v>
@@ -843,7 +846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" t="s">
         <v>56</v>
@@ -894,7 +897,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" t="s">
         <v>57</v>
@@ -945,7 +948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>0</v>
@@ -996,7 +999,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>1</v>
@@ -1047,7 +1050,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>2</v>
@@ -1067,33 +1070,33 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <f t="shared" ref="G6:G8" si="1">F8</f>
+        <f t="shared" ref="G8" si="1">F8</f>
         <v>3</v>
       </c>
       <c r="H8">
-        <f t="shared" ref="H6:H8" si="2">G8</f>
+        <f t="shared" ref="H8" si="2">G8</f>
         <v>3</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" ref="J6:J8" si="3">I8</f>
+        <f t="shared" ref="J8" si="3">I8</f>
         <v>3</v>
       </c>
       <c r="K8">
-        <f t="shared" ref="K6:K8" si="4">J8</f>
+        <f t="shared" ref="K8" si="4">J8</f>
         <v>3</v>
       </c>
       <c r="L8">
         <v>3</v>
       </c>
       <c r="M8">
-        <f t="shared" ref="M6:M8" si="5">L8</f>
+        <f t="shared" ref="M8" si="5">L8</f>
         <v>3</v>
       </c>
       <c r="N8">
-        <f t="shared" ref="N6:N8" si="6">M8</f>
+        <f t="shared" ref="N8" si="6">M8</f>
         <v>3</v>
       </c>
       <c r="O8">
@@ -1106,7 +1109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" t="s">
         <v>3</v>
@@ -1157,7 +1160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" t="s">
         <v>5</v>
@@ -1208,216 +1211,171 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>60</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>60</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>60</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>60</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G13" t="s">
         <v>60</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H13" t="s">
         <v>60</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I13" t="s">
         <v>60</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J13" t="s">
         <v>60</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K13" t="s">
         <v>60</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L13" t="s">
         <v>60</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M13" t="s">
         <v>60</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N13" t="s">
         <v>60</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O13" t="s">
         <v>60</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P13" t="s">
         <v>60</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="Q13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13">
-        <v>6</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13">
-        <v>6</v>
-      </c>
-      <c r="G13">
-        <v>6</v>
-      </c>
-      <c r="H13">
-        <v>6</v>
-      </c>
-      <c r="I13">
-        <v>6</v>
-      </c>
-      <c r="J13">
-        <v>6</v>
-      </c>
-      <c r="K13">
-        <v>6</v>
-      </c>
-      <c r="L13">
-        <v>6</v>
-      </c>
-      <c r="M13">
-        <v>6</v>
-      </c>
-      <c r="N13">
-        <v>6</v>
-      </c>
-      <c r="O13">
-        <v>6</v>
-      </c>
-      <c r="P13">
-        <v>6</v>
-      </c>
-      <c r="Q13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1465,522 +1423,522 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
         <v>13</v>
       </c>
-      <c r="C17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="D17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="E17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="F17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="G17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="H17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="I17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="J17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="K17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="L17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="M17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="N17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="O17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="P17" s="4">
-        <v>44831</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>44831</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>13</v>
+      </c>
+      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>13</v>
+      </c>
+      <c r="I17">
+        <v>13</v>
+      </c>
+      <c r="J17">
+        <v>13</v>
+      </c>
+      <c r="K17">
+        <v>13</v>
+      </c>
+      <c r="L17">
+        <v>13</v>
+      </c>
+      <c r="M17">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>13</v>
+      </c>
+      <c r="O17">
+        <v>13</v>
+      </c>
+      <c r="P17">
+        <v>13</v>
+      </c>
+      <c r="Q17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="C18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="D18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="E18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="F18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="G18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="H18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="I18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="J18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="K18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="L18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="M18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="N18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="O18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="P18" s="4">
+        <v>44831</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>44831</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="D19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="E19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="F19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="G19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="H19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="I19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="J19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="K19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="L19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="M19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="N19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="O19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="P19" s="4">
-        <v>44951</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>44951</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
       <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="D20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="E20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="F20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="G20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="H20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="I20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="J20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="K20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="L20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="M20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="N20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="O20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="P20" s="4">
+        <v>44951</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>44951</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
       <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>76</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>76</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>76</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G22" t="s">
         <v>76</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H22" t="s">
         <v>76</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I22" t="s">
         <v>76</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J22" t="s">
         <v>76</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K22" t="s">
         <v>76</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L22" t="s">
         <v>76</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M22" t="s">
         <v>76</v>
       </c>
-      <c r="N21" t="s">
+      <c r="N22" t="s">
         <v>76</v>
       </c>
-      <c r="O21" t="s">
+      <c r="O22" t="s">
         <v>76</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P22" t="s">
         <v>76</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="Q22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8"/>
-      <c r="B22" s="1" t="s">
+    <row r="23" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>59</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>59</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>59</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" t="s">
         <v>59</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G24" t="s">
         <v>59</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H24" t="s">
         <v>59</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I24" t="s">
         <v>59</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J24" t="s">
         <v>59</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K24" t="s">
         <v>59</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L24" t="s">
         <v>59</v>
       </c>
-      <c r="M23" t="s">
+      <c r="M24" t="s">
         <v>59</v>
       </c>
-      <c r="N23" t="s">
+      <c r="N24" t="s">
         <v>59</v>
       </c>
-      <c r="O23" t="s">
+      <c r="O24" t="s">
         <v>59</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P24" t="s">
         <v>59</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24">
-        <v>12</v>
-      </c>
-      <c r="D24">
-        <v>12</v>
-      </c>
-      <c r="E24">
-        <v>12</v>
-      </c>
-      <c r="F24">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>12</v>
-      </c>
-      <c r="H24">
-        <v>12</v>
-      </c>
-      <c r="I24">
-        <v>12</v>
-      </c>
-      <c r="J24">
-        <v>12</v>
-      </c>
-      <c r="K24">
-        <v>12</v>
-      </c>
-      <c r="L24">
-        <v>12</v>
-      </c>
-      <c r="M24">
-        <v>12</v>
-      </c>
-      <c r="N24">
-        <v>12</v>
-      </c>
-      <c r="O24">
-        <v>6</v>
-      </c>
-      <c r="P24">
-        <v>6</v>
-      </c>
-      <c r="Q24">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -2028,522 +1986,522 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="D28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="E28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="F28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="G28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="H28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="I28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="J28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="K28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="L28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="M28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="N28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="O28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="P28" s="4">
-        <v>45026</v>
-      </c>
-      <c r="Q28" s="4">
-        <v>45026</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="C28">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>15</v>
+      </c>
+      <c r="E28">
+        <v>15</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>15</v>
+      </c>
+      <c r="H28">
+        <v>15</v>
+      </c>
+      <c r="I28">
+        <v>15</v>
+      </c>
+      <c r="J28">
+        <v>15</v>
+      </c>
+      <c r="K28">
+        <v>15</v>
+      </c>
+      <c r="L28">
+        <v>15</v>
+      </c>
+      <c r="M28">
+        <v>15</v>
+      </c>
+      <c r="N28">
+        <v>15</v>
+      </c>
+      <c r="O28">
+        <v>15</v>
+      </c>
+      <c r="P28">
+        <v>15</v>
+      </c>
+      <c r="Q28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="C29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="D29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="E29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="F29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="G29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="H29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="I29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="J29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="K29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="L29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="M29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="N29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="O29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="P29" s="4">
+        <v>45026</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>45026</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="D30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="E30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="F30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="G30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="H30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="I30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="J30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="K30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="L30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="M30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="N30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="O30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="P30" s="4">
-        <v>45332</v>
-      </c>
-      <c r="Q30" s="4">
-        <v>45332</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="C31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="D31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="E31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="F31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="G31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="H31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="I31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="J31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="K31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="L31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="M31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="N31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="O31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="P31" s="4">
+        <v>45332</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>45332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="7"/>
+      <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I32" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" t="s">
-        <v>20</v>
-      </c>
-      <c r="O32" t="s">
-        <v>20</v>
-      </c>
-      <c r="P32" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-      <c r="B33" s="1" t="s">
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" t="s">
+        <v>20</v>
+      </c>
+      <c r="P33" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+      <c r="C34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>33</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>34</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>34</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E35" t="s">
         <v>34</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>34</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G35" t="s">
         <v>34</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H35" t="s">
         <v>34</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I35" t="s">
         <v>34</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J35" t="s">
         <v>34</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K35" t="s">
         <v>34</v>
       </c>
-      <c r="L34" t="s">
+      <c r="L35" t="s">
         <v>34</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M35" t="s">
         <v>34</v>
       </c>
-      <c r="N34" t="s">
+      <c r="N35" t="s">
         <v>34</v>
       </c>
-      <c r="O34" t="s">
+      <c r="O35" t="s">
         <v>34</v>
       </c>
-      <c r="P34" t="s">
+      <c r="P35" t="s">
         <v>34</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="Q35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35">
-        <v>10</v>
-      </c>
-      <c r="D35">
-        <v>10</v>
-      </c>
-      <c r="E35">
-        <v>10</v>
-      </c>
-      <c r="F35">
-        <v>10</v>
-      </c>
-      <c r="G35">
-        <v>10</v>
-      </c>
-      <c r="H35">
-        <v>10</v>
-      </c>
-      <c r="I35">
-        <v>10</v>
-      </c>
-      <c r="J35">
-        <v>10</v>
-      </c>
-      <c r="K35">
-        <v>10</v>
-      </c>
-      <c r="L35">
-        <v>10</v>
-      </c>
-      <c r="M35">
-        <v>10</v>
-      </c>
-      <c r="N35">
-        <v>10</v>
-      </c>
-      <c r="O35">
-        <v>10</v>
-      </c>
-      <c r="P35">
-        <v>10</v>
-      </c>
-      <c r="Q35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2591,10 +2549,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="8"/>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2642,318 +2600,369 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
       <c r="B39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="D39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="E39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="F39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="G39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="H39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="I39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="J39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="K39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="L39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="M39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="N39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="O39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="P39" s="4">
-        <v>45352</v>
-      </c>
-      <c r="Q39" s="4">
-        <v>45352</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
       <c r="B40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+      <c r="C40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="D40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="E40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="F40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="G40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="H40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="I40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="J40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="K40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="L40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="M40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="N40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="O40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="P40" s="4">
+        <v>45352</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="D41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="E41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="F41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="G41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="H41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="I41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="J41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="K41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="L41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="M41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="N41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="O41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="P41" s="4">
-        <v>45566</v>
-      </c>
-      <c r="Q41" s="4">
-        <v>45566</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="C42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="D42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="E42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="F42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="G42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="H42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="I42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="J42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="K42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="L42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="M42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="N42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="O42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="P42" s="4">
+        <v>45566</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" t="s">
         <v>43</v>
       </c>
-      <c r="C43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
-        <v>20</v>
-      </c>
-      <c r="H43" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" t="s">
-        <v>20</v>
-      </c>
-      <c r="L43" t="s">
-        <v>20</v>
-      </c>
-      <c r="M43" t="s">
-        <v>20</v>
-      </c>
-      <c r="N43" t="s">
-        <v>20</v>
-      </c>
-      <c r="O43" t="s">
-        <v>20</v>
-      </c>
-      <c r="P43" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="9"/>
-      <c r="B44" s="1" t="s">
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s">
+        <v>20</v>
+      </c>
+      <c r="L44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" t="s">
+        <v>20</v>
+      </c>
+      <c r="O44" t="s">
+        <v>20</v>
+      </c>
+      <c r="P44" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q44" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q45" s="1" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A6:A11"/>
-    <mergeCell ref="A12:A22"/>
-    <mergeCell ref="A23:A33"/>
-    <mergeCell ref="A34:A44"/>
+    <mergeCell ref="A6:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="A35:A45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
